--- a/examples/Differentiation/Tables/note_02_core_formation.xlsx
+++ b/examples/Differentiation/Tables/note_02_core_formation.xlsx
@@ -5642,25 +5642,25 @@
         <v>0.02162380874236644</v>
       </c>
       <c r="G127" t="n">
-        <v>0.04776045399645228</v>
+        <v>0.04326882239409099</v>
       </c>
       <c r="H127" t="n">
-        <v>0.001965886672138816</v>
+        <v>0.00105855895354241</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2975923835032065</v>
+        <v>0.3048168234071141</v>
       </c>
       <c r="J127" t="n">
-        <v>0.2320881929548722</v>
+        <v>0.2365798245572335</v>
       </c>
       <c r="K127" t="n">
-        <v>0.01352938235672406</v>
+        <v>0.01443671007532047</v>
       </c>
       <c r="L127" t="n">
-        <v>0.02900915562194558</v>
+        <v>0.02178471571803798</v>
       </c>
       <c r="M127" t="n">
-        <v>0.01604214839376667</v>
+        <v>0.006992227906909217</v>
       </c>
     </row>
     <row r="128">
@@ -5683,25 +5683,25 @@
         <v>0.02161462703726158</v>
       </c>
       <c r="G128" t="n">
-        <v>0.04815608651044235</v>
+        <v>0.04367695058307871</v>
       </c>
       <c r="H128" t="n">
-        <v>0.001970597317334818</v>
+        <v>0.001070801807493594</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2978265217332062</v>
+        <v>0.3050272099159564</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2315424398291656</v>
+        <v>0.2360215757565293</v>
       </c>
       <c r="K128" t="n">
-        <v>0.01351521802240231</v>
+        <v>0.01441501353224353</v>
       </c>
       <c r="L128" t="n">
-        <v>0.02892235003595105</v>
+        <v>0.02172166185320093</v>
       </c>
       <c r="M128" t="n">
-        <v>0.01600324920857722</v>
+        <v>0.006980804280281884</v>
       </c>
     </row>
     <row r="129">
@@ -5724,25 +5724,25 @@
         <v>0.02160923413083896</v>
       </c>
       <c r="G129" t="n">
-        <v>0.04854084511540379</v>
+        <v>0.04408619610050966</v>
       </c>
       <c r="H129" t="n">
-        <v>0.001954274213843228</v>
+        <v>0.00107448073142029</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2981113853611148</v>
+        <v>0.3052641838859264</v>
       </c>
       <c r="J129" t="n">
-        <v>0.2309915695673394</v>
+        <v>0.2354462185822335</v>
       </c>
       <c r="K129" t="n">
-        <v>0.01352077137120551</v>
+        <v>0.01440056485362844</v>
       </c>
       <c r="L129" t="n">
-        <v>0.02876735474013998</v>
+        <v>0.02161455621532845</v>
       </c>
       <c r="M129" t="n">
-        <v>0.01594724882169963</v>
+        <v>0.006976094269393678</v>
       </c>
     </row>
     <row r="130">
@@ -5847,25 +5847,25 @@
         <v>0.02160209023536509</v>
       </c>
       <c r="G132" t="n">
-        <v>0.04876781743451317</v>
+        <v>0.04432432322471557</v>
       </c>
       <c r="H132" t="n">
-        <v>0.001962719007241097</v>
+        <v>0.001085128599580907</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2982885612566266</v>
+        <v>0.3054234485895189</v>
       </c>
       <c r="J132" t="n">
-        <v>0.2306479899273803</v>
+        <v>0.235091484137178</v>
       </c>
       <c r="K132" t="n">
-        <v>0.01350498412713658</v>
+        <v>0.01438257453479677</v>
       </c>
       <c r="L132" t="n">
-        <v>0.02870470362175674</v>
+        <v>0.02156981628886453</v>
       </c>
       <c r="M132" t="n">
-        <v>0.01600206154145263</v>
+        <v>0.007053371493126044</v>
       </c>
     </row>
     <row r="133">
@@ -5888,25 +5888,25 @@
         <v>0.02159957238416908</v>
       </c>
       <c r="G133" t="n">
-        <v>0.04884762150650495</v>
+        <v>0.04440805878471082</v>
       </c>
       <c r="H133" t="n">
-        <v>0.001965697357828347</v>
+        <v>0.001088883419315359</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2983509700318643</v>
+        <v>0.3054795446021803</v>
       </c>
       <c r="J133" t="n">
-        <v>0.2305270878461387</v>
+        <v>0.2349666505679328</v>
       </c>
       <c r="K133" t="n">
-        <v>0.01349941794498441</v>
+        <v>0.0143762318834974</v>
       </c>
       <c r="L133" t="n">
-        <v>0.02868265886753828</v>
+        <v>0.02155408429722233</v>
       </c>
       <c r="M133" t="n">
-        <v>0.01602164302941636</v>
+        <v>0.007080870549091603</v>
       </c>
     </row>
     <row r="134">
@@ -5929,25 +5929,25 @@
         <v>0.0215971014140463</v>
       </c>
       <c r="G134" t="n">
-        <v>0.04892586970802617</v>
+        <v>0.0444901652719838</v>
       </c>
       <c r="H134" t="n">
-        <v>0.001968620506921805</v>
+        <v>0.001092568580106344</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2984122039612792</v>
+        <v>0.3055345833093585</v>
       </c>
       <c r="J134" t="n">
-        <v>0.2304085068588186</v>
+        <v>0.234844211294861</v>
       </c>
       <c r="K134" t="n">
-        <v>0.01349395514839716</v>
+        <v>0.01437000707521262</v>
       </c>
       <c r="L134" t="n">
-        <v>0.02866103740216883</v>
+        <v>0.02153865805408952</v>
       </c>
       <c r="M134" t="n">
-        <v>0.0160409552809294</v>
+        <v>0.007107952947628638</v>
       </c>
     </row>
     <row r="135">
@@ -5970,25 +5970,25 @@
         <v>0.02159487371840738</v>
       </c>
       <c r="G135" t="n">
-        <v>0.04899635130103064</v>
+        <v>0.04456412529083555</v>
       </c>
       <c r="H135" t="n">
-        <v>0.001971256022969672</v>
+        <v>0.001095891085494852</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2984673977927489</v>
+        <v>0.3055841918569627</v>
       </c>
       <c r="J135" t="n">
-        <v>0.2303016633647934</v>
+        <v>0.2347338893749885</v>
       </c>
       <c r="K135" t="n">
-        <v>0.01348903002083429</v>
+        <v>0.01436439495830911</v>
       </c>
       <c r="L135" t="n">
-        <v>0.02864155606782222</v>
+        <v>0.02152476200360834</v>
       </c>
       <c r="M135" t="n">
-        <v>0.01605845172408325</v>
+        <v>0.007132454543325448</v>
       </c>
     </row>
     <row r="136">
@@ -6011,25 +6011,25 @@
         <v>0.02157811487288836</v>
       </c>
       <c r="G136" t="n">
-        <v>0.04952622886005904</v>
+        <v>0.04512017087767051</v>
       </c>
       <c r="H136" t="n">
-        <v>0.001991087905460454</v>
+        <v>0.001120891155251365</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2988825414656888</v>
+        <v>0.3059573177120979</v>
       </c>
       <c r="J136" t="n">
-        <v>0.2294982369998433</v>
+        <v>0.2339042949822319</v>
       </c>
       <c r="K136" t="n">
-        <v>0.01345197350271197</v>
+        <v>0.01432217025292105</v>
       </c>
       <c r="L136" t="n">
-        <v>0.0284950757669904</v>
+        <v>0.02142029952058129</v>
       </c>
       <c r="M136" t="n">
-        <v>0.01619057726385514</v>
+        <v>0.007317279503634572</v>
       </c>
     </row>
     <row r="137">
@@ -6052,25 +6052,25 @@
         <v>0.02157382028323094</v>
       </c>
       <c r="G137" t="n">
-        <v>0.04952417717410661</v>
+        <v>0.04512078213424582</v>
       </c>
       <c r="H137" t="n">
-        <v>0.001991249189434891</v>
+        <v>0.001121578370555552</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2988985580625239</v>
+        <v>0.3059690584408858</v>
       </c>
       <c r="J137" t="n">
-        <v>0.2294975215410789</v>
+        <v>0.2339009165809397</v>
       </c>
       <c r="K137" t="n">
-        <v>0.01345191838531921</v>
+        <v>0.01432158920419854</v>
       </c>
       <c r="L137" t="n">
-        <v>0.02851075900481802</v>
+        <v>0.02144025862645607</v>
       </c>
       <c r="M137" t="n">
-        <v>0.01619770866490088</v>
+        <v>0.007329773766917134</v>
       </c>
     </row>
     <row r="138">
@@ -6093,25 +6093,25 @@
         <v>0.02155536484044202</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0498624459888215</v>
+        <v>0.04548207167647841</v>
       </c>
       <c r="H138" t="n">
-        <v>0.002004968381898577</v>
+        <v>0.001139844158264561</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2992519856512198</v>
+        <v>0.3062855218096672</v>
       </c>
       <c r="J138" t="n">
-        <v>0.2289545488479352</v>
+        <v>0.2333349231602783</v>
       </c>
       <c r="K138" t="n">
-        <v>0.01342571157337829</v>
+        <v>0.0142908357970123</v>
       </c>
       <c r="L138" t="n">
-        <v>0.02839993280078338</v>
+        <v>0.02136639664233598</v>
       </c>
       <c r="M138" t="n">
-        <v>0.01630193816783177</v>
+        <v>0.007480364386914092</v>
       </c>
     </row>
     <row r="139">
@@ -6216,25 +6216,25 @@
         <v>0.02152816333912041</v>
       </c>
       <c r="G141" t="n">
-        <v>0.05098648828854375</v>
+        <v>0.04670186609783038</v>
       </c>
       <c r="H141" t="n">
-        <v>0.002052368246815386</v>
+        <v>0.001206155073694292</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3000961381053034</v>
+        <v>0.3069759257569547</v>
       </c>
       <c r="J141" t="n">
-        <v>0.2272910610573453</v>
+        <v>0.2315756832480587</v>
       </c>
       <c r="K141" t="n">
-        <v>0.01334340005005946</v>
+        <v>0.01418961322318055</v>
       </c>
       <c r="L141" t="n">
-        <v>0.02803236664685957</v>
+        <v>0.02115257899520826</v>
       </c>
       <c r="M141" t="n">
-        <v>0.01677764187070791</v>
+        <v>0.008148901931239768</v>
       </c>
     </row>
     <row r="142">
@@ -6257,25 +6257,25 @@
         <v>0.02151007926072384</v>
       </c>
       <c r="G142" t="n">
-        <v>0.05162276186224619</v>
+        <v>0.04736751787826595</v>
       </c>
       <c r="H142" t="n">
-        <v>0.002076808538625211</v>
+        <v>0.001236397563325463</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3005170226708368</v>
+        <v>0.3073496379430078</v>
       </c>
       <c r="J142" t="n">
-        <v>0.2264028732296773</v>
+        <v>0.2306581172136575</v>
       </c>
       <c r="K142" t="n">
-        <v>0.01330278085551288</v>
+        <v>0.01414319183081263</v>
       </c>
       <c r="L142" t="n">
-        <v>0.02786648922750422</v>
+        <v>0.02103387395533326</v>
       </c>
       <c r="M142" t="n">
-        <v>0.01703128163721915</v>
+        <v>0.008461706052157231</v>
       </c>
     </row>
     <row r="143">
@@ -6298,25 +6298,25 @@
         <v>0.021505652600049</v>
       </c>
       <c r="G143" t="n">
-        <v>0.05189042371613148</v>
+        <v>0.04765330856356727</v>
       </c>
       <c r="H143" t="n">
-        <v>0.002088085346442703</v>
+        <v>0.001251254816576578</v>
       </c>
       <c r="I143" t="n">
-        <v>0.300715365100163</v>
+        <v>0.3075188710355096</v>
       </c>
       <c r="J143" t="n">
-        <v>0.2259885006956547</v>
+        <v>0.230225615848219</v>
       </c>
       <c r="K143" t="n">
-        <v>0.01328196724263053</v>
+        <v>0.01411879777249666</v>
       </c>
       <c r="L143" t="n">
-        <v>0.02778043860162908</v>
+        <v>0.02097693266628255</v>
       </c>
       <c r="M143" t="n">
-        <v>0.01713442848449722</v>
+        <v>0.0086013622962345</v>
       </c>
     </row>
   </sheetData>
@@ -9284,31 +9284,31 @@
         <v>0.3432549756295737</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01518503056995583</v>
+        <v>0.01518503056995584</v>
       </c>
       <c r="F72" t="n">
         <v>0.02207734768401437</v>
       </c>
       <c r="G72" t="n">
-        <v>0.03051312314689466</v>
+        <v>0.03050663220720121</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0001598828788073737</v>
+        <v>0.0001375707088129389</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3094958789437565</v>
+        <v>0.3095231607097172</v>
       </c>
       <c r="J72" t="n">
-        <v>0.2508015652901827</v>
+        <v>0.2508080562298762</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01540292627783888</v>
+        <v>0.01542523844783331</v>
       </c>
       <c r="L72" t="n">
-        <v>0.01310926957897522</v>
+        <v>0.01308198781301444</v>
       </c>
       <c r="M72" t="n">
-        <v>0.001280454918936593</v>
+        <v>0.001254694496702905</v>
       </c>
     </row>
     <row r="73">
@@ -9322,34 +9322,34 @@
         <v>0.1977562737262718</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3431610382576716</v>
+        <v>0.3431610382576715</v>
       </c>
       <c r="E73" t="n">
-        <v>0.01512860795650217</v>
+        <v>0.01512860795650218</v>
       </c>
       <c r="F73" t="n">
         <v>0.02199841074614918</v>
       </c>
       <c r="G73" t="n">
-        <v>0.03270523054435174</v>
+        <v>0.0326962409842319</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0001587728778111515</v>
+        <v>0.0001370439280574026</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3106083359285304</v>
+        <v>0.3106348585009643</v>
       </c>
       <c r="J73" t="n">
-        <v>0.2480339195289949</v>
+        <v>0.2480429090891147</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01536929927558124</v>
+        <v>0.01539102822533498</v>
       </c>
       <c r="L73" t="n">
-        <v>0.01283638488440684</v>
+        <v>0.0128098623119729</v>
       </c>
       <c r="M73" t="n">
-        <v>0.001310038373739316</v>
+        <v>0.001287711738745022</v>
       </c>
     </row>
     <row r="74">
@@ -9410,28 +9410,28 @@
         <v>0.01505812801735759</v>
       </c>
       <c r="F75" t="n">
-        <v>0.02190638147252745</v>
+        <v>0.02190638147252744</v>
       </c>
       <c r="G75" t="n">
-        <v>0.03666288899045012</v>
+        <v>0.0366532154834149</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0001715270464715075</v>
+        <v>0.0001492175937794604</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3123681385962475</v>
+        <v>0.3123939021585609</v>
       </c>
       <c r="J75" t="n">
-        <v>0.2427201634304198</v>
+        <v>0.2427298369374551</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01527180696272897</v>
+        <v>0.01529411641542102</v>
       </c>
       <c r="L75" t="n">
-        <v>0.01247229592035492</v>
+        <v>0.01244653235804144</v>
       </c>
       <c r="M75" t="n">
-        <v>0.001333393696661113</v>
+        <v>0.001313849531761434</v>
       </c>
     </row>
     <row r="76">
@@ -9486,7 +9486,7 @@
         <v>0.2044065001664981</v>
       </c>
       <c r="D77" t="n">
-        <v>0.343206739866915</v>
+        <v>0.3432067398669151</v>
       </c>
       <c r="E77" t="n">
         <v>0.01503735449755585</v>
@@ -9495,25 +9495,25 @@
         <v>0.02187464106483782</v>
       </c>
       <c r="G77" t="n">
-        <v>0.03642206767261489</v>
+        <v>0.03641221120190968</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0001678933923102256</v>
+        <v>0.0001461998398972016</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3126279967740097</v>
+        <v>0.3126534167938534</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2429399054164499</v>
+        <v>0.2429497618871552</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01527618945955487</v>
+        <v>0.0152978830119679</v>
       </c>
       <c r="L77" t="n">
-        <v>0.01244721185575065</v>
+        <v>0.01242179183590707</v>
       </c>
       <c r="M77" t="n">
-        <v>0.001332421476325073</v>
+        <v>0.001313131459756156</v>
       </c>
     </row>
     <row r="78">
@@ -9568,34 +9568,34 @@
         <v>0.2050642723942703</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3432300558483935</v>
+        <v>0.3432300558483936</v>
       </c>
       <c r="E79" t="n">
-        <v>0.01502968289175896</v>
+        <v>0.01502968289175897</v>
       </c>
       <c r="F79" t="n">
         <v>0.02186463865983652</v>
       </c>
       <c r="G79" t="n">
-        <v>0.03685920811784914</v>
+        <v>0.03684923868996695</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0001688540947501943</v>
+        <v>0.0001472660342259998</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3128203171895755</v>
+        <v>0.3128456531497075</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2423539418677699</v>
+        <v>0.2423639112956522</v>
       </c>
       <c r="K79" t="n">
-        <v>0.01526592265699274</v>
+        <v>0.01528751071751693</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0124073786730724</v>
+        <v>0.0123820427129405</v>
       </c>
       <c r="M79" t="n">
-        <v>0.001333719284732969</v>
+        <v>0.001314604852875557</v>
       </c>
     </row>
     <row r="80">
@@ -9609,7 +9609,7 @@
         <v>0.2061648318348297</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3432687345414073</v>
+        <v>0.3432687345414075</v>
       </c>
       <c r="E80" t="n">
         <v>0.01501695652697716</v>
@@ -9618,25 +9618,25 @@
         <v>0.02184804575111413</v>
       </c>
       <c r="G80" t="n">
-        <v>0.03758359973445354</v>
+        <v>0.03757352126014159</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0001707938567319179</v>
+        <v>0.0001492545844178455</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3131393921581384</v>
+        <v>0.3131645903361846</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2413826688090585</v>
+        <v>0.2413927472833705</v>
       </c>
       <c r="K80" t="n">
-        <v>0.01524854508081847</v>
+        <v>0.01527008435313254</v>
       </c>
       <c r="L80" t="n">
-        <v>0.01234126354129944</v>
+        <v>0.01231606536325324</v>
       </c>
       <c r="M80" t="n">
-        <v>0.001336230904328783</v>
+        <v>0.001317452294862414</v>
       </c>
     </row>
     <row r="81">
@@ -9691,34 +9691,34 @@
         <v>0.2070429736929715</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3432993015170395</v>
+        <v>0.3432993015170396</v>
       </c>
       <c r="E82" t="n">
-        <v>0.01500689914261744</v>
+        <v>0.01500689914261745</v>
       </c>
       <c r="F82" t="n">
-        <v>0.02183493271659657</v>
+        <v>0.02183493271659656</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03815629505509469</v>
+        <v>0.03814611415209535</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0001722366825666499</v>
+        <v>0.0001507686872348817</v>
       </c>
       <c r="I82" t="n">
-        <v>0.313391540235358</v>
+        <v>0.3134166290275303</v>
       </c>
       <c r="J82" t="n">
-        <v>0.2406148681620243</v>
+        <v>0.2406250490650237</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01523490206791773</v>
+        <v>0.0152563700632495</v>
       </c>
       <c r="L82" t="n">
-        <v>0.01228902442078389</v>
+        <v>0.01226393562861176</v>
       </c>
       <c r="M82" t="n">
-        <v>0.001338103006940752</v>
+        <v>0.001319574320927589</v>
       </c>
     </row>
     <row r="83">
@@ -9814,34 +9814,34 @@
         <v>0.2085146253746231</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3433499505181524</v>
+        <v>0.3433499505181525</v>
       </c>
       <c r="E85" t="n">
         <v>0.01499023421384737</v>
       </c>
       <c r="F85" t="n">
-        <v>0.02181320462324957</v>
+        <v>0.02181320462324956</v>
       </c>
       <c r="G85" t="n">
-        <v>0.03907820502802747</v>
+        <v>0.03906809597966659</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0001857874896651006</v>
+        <v>0.000164471010858252</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3138093126982716</v>
+        <v>0.3138342244191082</v>
       </c>
       <c r="J85" t="n">
-        <v>0.2393696717111454</v>
+        <v>0.2393797807595063</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01520113574143921</v>
+        <v>0.01522245222024605</v>
       </c>
       <c r="L85" t="n">
-        <v>0.01220249797620082</v>
+        <v>0.0121775862553642</v>
       </c>
       <c r="M85" t="n">
-        <v>0.001357148135447402</v>
+        <v>0.001338750220941902</v>
       </c>
     </row>
     <row r="86">
@@ -9855,34 +9855,34 @@
         <v>0.2099728937728914</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3433994385954742</v>
+        <v>0.3433994385954743</v>
       </c>
       <c r="E86" t="n">
         <v>0.0149739512612636</v>
       </c>
       <c r="F86" t="n">
-        <v>0.02179197455868786</v>
+        <v>0.02179197455868785</v>
       </c>
       <c r="G86" t="n">
-        <v>0.03997920356167481</v>
+        <v>0.039969164720975</v>
       </c>
       <c r="H86" t="n">
-        <v>0.000199122191472032</v>
+        <v>0.000177953756285709</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3142175087345548</v>
+        <v>0.3142422474427011</v>
       </c>
       <c r="J86" t="n">
-        <v>0.2381527967363804</v>
+        <v>0.2381628355770803</v>
       </c>
       <c r="K86" t="n">
-        <v>0.01516804887938824</v>
+        <v>0.01518921731457456</v>
       </c>
       <c r="L86" t="n">
-        <v>0.01211795548110298</v>
+        <v>0.01209321677295667</v>
       </c>
       <c r="M86" t="n">
-        <v>0.001375443976010106</v>
+        <v>0.001357173835603612</v>
       </c>
     </row>
     <row r="87">
@@ -9937,34 +9937,34 @@
         <v>0.2162077355977331</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3438027815692332</v>
+        <v>0.3438027815692333</v>
       </c>
       <c r="E88" t="n">
         <v>0.01497068833747787</v>
       </c>
       <c r="F88" t="n">
-        <v>0.02179584926717562</v>
+        <v>0.02179584926717561</v>
       </c>
       <c r="G88" t="n">
-        <v>0.04211991028582016</v>
+        <v>0.04211016093792548</v>
       </c>
       <c r="H88" t="n">
-        <v>0.00021840396110095</v>
+        <v>0.0001978459658912599</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3149450522065073</v>
+        <v>0.3149690775177355</v>
       </c>
       <c r="J88" t="n">
-        <v>0.23527598769583</v>
+        <v>0.2352857370437247</v>
       </c>
       <c r="K88" t="n">
-        <v>0.01509921445092405</v>
+        <v>0.01511977244613374</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0117721122259298</v>
+        <v>0.01174808691470158</v>
       </c>
       <c r="M88" t="n">
-        <v>0.001479374357269387</v>
+        <v>0.001461631077917319</v>
       </c>
     </row>
     <row r="89">
@@ -9978,34 +9978,34 @@
         <v>0.2168986813186788</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3438240383919988</v>
+        <v>0.3438240383919989</v>
       </c>
       <c r="E89" t="n">
         <v>0.01496328188618692</v>
       </c>
       <c r="F89" t="n">
-        <v>0.02178616668091139</v>
+        <v>0.02178616668091138</v>
       </c>
       <c r="G89" t="n">
-        <v>0.04252303031315022</v>
+        <v>0.04251331202247622</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0002246098341677578</v>
+        <v>0.0002041173278708404</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3151286636821976</v>
+        <v>0.3151526124591386</v>
       </c>
       <c r="J89" t="n">
-        <v>0.2347313316175139</v>
+        <v>0.234741049908188</v>
       </c>
       <c r="K89" t="n">
-        <v>0.01508416937000535</v>
+        <v>0.01510466187630227</v>
       </c>
       <c r="L89" t="n">
-        <v>0.01173470822386704</v>
+        <v>0.0117107594469261</v>
       </c>
       <c r="M89" t="n">
-        <v>0.001487653263035063</v>
+        <v>0.001469966506124116</v>
       </c>
     </row>
     <row r="90">
@@ -10019,34 +10019,34 @@
         <v>0.2424362637362609</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3436879906537424</v>
+        <v>0.3436879906537425</v>
       </c>
       <c r="E90" t="n">
         <v>0.01481668729031247</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0215829802098944</v>
+        <v>0.02158298020989439</v>
       </c>
       <c r="G90" t="n">
-        <v>0.04571718981333123</v>
+        <v>0.04573002314470628</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0002010227647069203</v>
+        <v>0.000164538060679574</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3187829939085468</v>
+        <v>0.3188130384578237</v>
       </c>
       <c r="J90" t="n">
-        <v>0.229666733930582</v>
+        <v>0.229653900599207</v>
       </c>
       <c r="K90" t="n">
-        <v>0.01499636995489399</v>
+        <v>0.01503285465892133</v>
       </c>
       <c r="L90" t="n">
-        <v>0.01054803147398893</v>
+        <v>0.01051798692471204</v>
       </c>
       <c r="M90" t="n">
-        <v>0.001561189154395211</v>
+        <v>0.001524751428493703</v>
       </c>
     </row>
     <row r="91">
@@ -10101,34 +10101,34 @@
         <v>0.2446318548118519</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3437489102865937</v>
+        <v>0.3437489102865938</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01479720238631991</v>
+        <v>0.01479720238631992</v>
       </c>
       <c r="F92" t="n">
-        <v>0.02155761082538051</v>
+        <v>0.0215576108253805</v>
       </c>
       <c r="G92" t="n">
-        <v>0.04685323233042121</v>
+        <v>0.04686548935226442</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0002041223167814259</v>
+        <v>0.0001678560938765526</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3192660042954677</v>
+        <v>0.3192957761696579</v>
       </c>
       <c r="J92" t="n">
-        <v>0.228149982698479</v>
+        <v>0.2281377256766358</v>
       </c>
       <c r="K92" t="n">
-        <v>0.01496944568677088</v>
+        <v>0.01500571190967575</v>
       </c>
       <c r="L92" t="n">
-        <v>0.01045348917378492</v>
+        <v>0.01042371729959472</v>
       </c>
       <c r="M92" t="n">
-        <v>0.001565459030599482</v>
+        <v>0.001529924483280734</v>
       </c>
     </row>
     <row r="93">
@@ -10145,31 +10145,31 @@
         <v>0.3434295403675005</v>
       </c>
       <c r="E93" t="n">
-        <v>0.01476133105224829</v>
+        <v>0.0147613310522483</v>
       </c>
       <c r="F93" t="n">
-        <v>0.02150197597238835</v>
+        <v>0.02150197597238834</v>
       </c>
       <c r="G93" t="n">
-        <v>0.04609239937309798</v>
+        <v>0.04610568690919457</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0001978919860003714</v>
+        <v>0.0001629137836203179</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3197058972784767</v>
+        <v>0.3197338954051449</v>
       </c>
       <c r="J93" t="n">
-        <v>0.228939654708188</v>
+        <v>0.2289263671720914</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01498145192932729</v>
+        <v>0.01501643013170734</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0103898573327718</v>
+        <v>0.01036185920610363</v>
       </c>
       <c r="M93" t="n">
-        <v>0.001558314372048402</v>
+        <v>0.00152400878499552</v>
       </c>
     </row>
     <row r="94">
@@ -10183,34 +10183,34 @@
         <v>0.2528721611721579</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3435368344882634</v>
+        <v>0.3435368344882635</v>
       </c>
       <c r="E94" t="n">
-        <v>0.01472911515480493</v>
+        <v>0.01472911515480494</v>
       </c>
       <c r="F94" t="n">
         <v>0.02146016679448999</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0479512864092508</v>
+        <v>0.04796437160981729</v>
       </c>
       <c r="H94" t="n">
-        <v>0.000231910266934976</v>
+        <v>0.0001974646940107387</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3205110358316865</v>
+        <v>0.3205386076177781</v>
       </c>
       <c r="J94" t="n">
-        <v>0.2264402008002946</v>
+        <v>0.2264271155997282</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01490728656220436</v>
+        <v>0.0149417321351286</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0102321636920696</v>
+        <v>0.01020459190597802</v>
       </c>
       <c r="M94" t="n">
-        <v>0.00160034711285573</v>
+        <v>0.001566563913030324</v>
       </c>
     </row>
     <row r="95">
@@ -10233,25 +10233,25 @@
         <v>0.02116202206184473</v>
       </c>
       <c r="G95" t="n">
-        <v>0.05449632923968374</v>
+        <v>0.05249883302331015</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0008826121182107592</v>
+        <v>0.0004267527386174362</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3247694859549687</v>
+        <v>0.326443767392438</v>
       </c>
       <c r="J95" t="n">
-        <v>0.2172410546915407</v>
+        <v>0.2192385509079143</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01409651877991788</v>
+        <v>0.01455237815951121</v>
       </c>
       <c r="L95" t="n">
-        <v>0.009484795963217437</v>
+        <v>0.007810514525748056</v>
       </c>
       <c r="M95" t="n">
-        <v>0.002799345709936353</v>
+        <v>0.001904138430964507</v>
       </c>
     </row>
     <row r="96">
@@ -10271,28 +10271,28 @@
         <v>0.0145109327890964</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02115818958026103</v>
+        <v>0.02115818958026102</v>
       </c>
       <c r="G96" t="n">
-        <v>0.05505101129297436</v>
+        <v>0.05305834512828328</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0009099760443728607</v>
+        <v>0.0004552201242632709</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3247774933130794</v>
+        <v>0.3264477270877705</v>
       </c>
       <c r="J96" t="n">
-        <v>0.216719155854438</v>
+        <v>0.2187118220191291</v>
       </c>
       <c r="K96" t="n">
-        <v>0.01407054618627537</v>
+        <v>0.01452530210638496</v>
       </c>
       <c r="L96" t="n">
-        <v>0.009461866008709277</v>
+        <v>0.007791632234018079</v>
       </c>
       <c r="M96" t="n">
-        <v>0.002803978460144233</v>
+        <v>0.001910932995562505</v>
       </c>
     </row>
     <row r="97">
@@ -10312,28 +10312,28 @@
         <v>0.01450826103183894</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02115435940146725</v>
+        <v>0.02115435940146724</v>
       </c>
       <c r="G97" t="n">
-        <v>0.05560534954211945</v>
+        <v>0.05361750953300212</v>
       </c>
       <c r="H97" t="n">
-        <v>0.000937322656258731</v>
+        <v>0.0004836681363020707</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3247854958867165</v>
+        <v>0.326451684423834</v>
       </c>
       <c r="J97" t="n">
-        <v>0.2161975811233144</v>
+        <v>0.2181854211324318</v>
       </c>
       <c r="K97" t="n">
-        <v>0.01404459007091121</v>
+        <v>0.01449824459086787</v>
       </c>
       <c r="L97" t="n">
-        <v>0.009438949805085509</v>
+        <v>0.007772761267967972</v>
       </c>
       <c r="M97" t="n">
-        <v>0.002808619762544962</v>
+        <v>0.00191773721738389</v>
       </c>
     </row>
   </sheetData>
